--- a/source_data/Cruaud_taxonomy_coi_min_bc_cov_300_seq_meta_updated.xlsx
+++ b/source_data/Cruaud_taxonomy_coi_min_bc_cov_300_seq_meta_updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ronquist/dev/ms-repos-iba/paper-mg-insects/source_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED0B229-0A33-5040-806F-E5E7B5792459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D6F668-0F95-C342-B9A3-2E1436F56B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="500" windowWidth="28480" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5280" yWindow="500" windowWidth="28480" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cruaud_taxonomy_coi_min_bc_cov_" sheetId="1" r:id="rId1"/>
@@ -8774,9 +8774,6 @@
     <t>Enoggerinae_i_s</t>
   </si>
   <si>
-    <t>Neanastatinae_i_s</t>
-  </si>
-  <si>
     <t>Ditropinotellinae_i_s</t>
   </si>
   <si>
@@ -8826,6 +8823,9 @@
   </si>
   <si>
     <t>Storyeinae</t>
+  </si>
+  <si>
+    <t>Eopelma_i_s</t>
   </si>
 </sst>
 </file>
@@ -9327,7 +9327,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -9336,7 +9336,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -26746,7 +26745,7 @@
         <v>1217</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>2917</v>
+        <v>2934</v>
       </c>
       <c r="V120" t="s">
         <v>59</v>
@@ -32094,7 +32093,7 @@
     </row>
     <row r="157" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B157" t="s">
         <v>2911</v>
@@ -32231,7 +32230,7 @@
     </row>
     <row r="158" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B158" t="s">
         <v>2911</v>
@@ -32368,7 +32367,7 @@
     </row>
     <row r="159" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B159" t="s">
         <v>2911</v>
@@ -32511,7 +32510,7 @@
     </row>
     <row r="160" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B160" t="s">
         <v>2911</v>
@@ -32651,7 +32650,7 @@
     </row>
     <row r="161" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B161" t="s">
         <v>2911</v>
@@ -32794,7 +32793,7 @@
     </row>
     <row r="162" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B162" t="s">
         <v>2911</v>
@@ -32934,7 +32933,7 @@
     </row>
     <row r="163" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B163" t="s">
         <v>2911</v>
@@ -33074,7 +33073,7 @@
     </row>
     <row r="164" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B164" t="s">
         <v>2911</v>
@@ -33214,7 +33213,7 @@
     </row>
     <row r="165" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B165" t="s">
         <v>2911</v>
@@ -33354,7 +33353,7 @@
     </row>
     <row r="166" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B166" t="s">
         <v>2911</v>
@@ -33491,7 +33490,7 @@
     </row>
     <row r="167" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B167" t="s">
         <v>2911</v>
@@ -33631,7 +33630,7 @@
     </row>
     <row r="168" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B168" t="s">
         <v>2911</v>
@@ -33771,7 +33770,7 @@
     </row>
     <row r="169" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B169" t="s">
         <v>2911</v>
@@ -33911,7 +33910,7 @@
     </row>
     <row r="170" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B170" t="s">
         <v>2911</v>
@@ -34048,7 +34047,7 @@
     </row>
     <row r="171" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B171" t="s">
         <v>2911</v>
@@ -34188,7 +34187,7 @@
     </row>
     <row r="172" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B172" t="s">
         <v>2911</v>
@@ -34337,7 +34336,7 @@
     </row>
     <row r="173" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B173" t="s">
         <v>2911</v>
@@ -34486,7 +34485,7 @@
     </row>
     <row r="174" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B174" t="s">
         <v>2911</v>
@@ -34635,7 +34634,7 @@
     </row>
     <row r="175" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B175" t="s">
         <v>2911</v>
@@ -34787,7 +34786,7 @@
     </row>
     <row r="176" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>2907</v>
@@ -34829,7 +34828,7 @@
         <v>2008</v>
       </c>
       <c r="S176" s="2" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="T176" t="s">
         <v>2008</v>
@@ -37295,7 +37294,7 @@
     </row>
     <row r="194" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B194" t="s">
         <v>2911</v>
@@ -37426,7 +37425,7 @@
     </row>
     <row r="195" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B195" t="s">
         <v>2911</v>
@@ -37557,7 +37556,7 @@
     </row>
     <row r="196" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B196" t="s">
         <v>2911</v>
@@ -37691,7 +37690,7 @@
     </row>
     <row r="197" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B197" t="s">
         <v>2911</v>
@@ -37825,7 +37824,7 @@
     </row>
     <row r="198" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B198" t="s">
         <v>2896</v>
@@ -37968,7 +37967,7 @@
     </row>
     <row r="199" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B199" t="s">
         <v>2896</v>
@@ -38108,7 +38107,7 @@
     </row>
     <row r="200" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B200" t="s">
         <v>2896</v>
@@ -38251,7 +38250,7 @@
     </row>
     <row r="201" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B201" t="s">
         <v>2896</v>
@@ -38400,7 +38399,7 @@
     </row>
     <row r="202" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B202" t="s">
         <v>2896</v>
@@ -38546,7 +38545,7 @@
     </row>
     <row r="203" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B203" t="s">
         <v>2896</v>
@@ -38692,7 +38691,7 @@
     </row>
     <row r="204" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B204" t="s">
         <v>2896</v>
@@ -38838,7 +38837,7 @@
     </row>
     <row r="205" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B205" t="s">
         <v>2896</v>
@@ -38984,7 +38983,7 @@
     </row>
     <row r="206" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B206" t="s">
         <v>2896</v>
@@ -39130,7 +39129,7 @@
     </row>
     <row r="207" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B207" t="s">
         <v>2896</v>
@@ -39276,7 +39275,7 @@
     </row>
     <row r="208" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B208" t="s">
         <v>2896</v>
@@ -39425,7 +39424,7 @@
     </row>
     <row r="209" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B209" t="s">
         <v>2896</v>
@@ -39574,7 +39573,7 @@
     </row>
     <row r="210" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B210" t="s">
         <v>2896</v>
@@ -39720,7 +39719,7 @@
     </row>
     <row r="211" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B211" t="s">
         <v>2896</v>
@@ -39866,7 +39865,7 @@
     </row>
     <row r="212" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B212" t="s">
         <v>2896</v>
@@ -39997,7 +39996,7 @@
     </row>
     <row r="213" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B213" t="s">
         <v>2896</v>
@@ -40131,7 +40130,7 @@
     </row>
     <row r="214" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B214" t="s">
         <v>2896</v>
@@ -40268,7 +40267,7 @@
     </row>
     <row r="215" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B215" t="s">
         <v>2896</v>
@@ -40399,7 +40398,7 @@
     </row>
     <row r="216" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B216" t="s">
         <v>2896</v>
@@ -43259,7 +43258,7 @@
     </row>
     <row r="236" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A236" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B236" t="s">
         <v>2911</v>
@@ -43402,7 +43401,7 @@
     </row>
     <row r="237" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A237" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B237" t="s">
         <v>2911</v>
@@ -43542,7 +43541,7 @@
     </row>
     <row r="238" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A238" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B238" t="s">
         <v>2911</v>
@@ -43673,7 +43672,7 @@
     </row>
     <row r="239" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A239" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B239" t="s">
         <v>2911</v>
@@ -43807,7 +43806,7 @@
     </row>
     <row r="240" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A240" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B240" t="s">
         <v>2911</v>
@@ -43941,7 +43940,7 @@
     </row>
     <row r="241" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A241" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B241" t="s">
         <v>2911</v>
@@ -44072,7 +44071,7 @@
     </row>
     <row r="242" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A242" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B242" t="s">
         <v>2911</v>
@@ -44206,7 +44205,7 @@
     </row>
     <row r="243" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A243" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B243" t="s">
         <v>2896</v>
@@ -44340,7 +44339,7 @@
     </row>
     <row r="244" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A244" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B244" t="s">
         <v>2896</v>
@@ -44474,7 +44473,7 @@
     </row>
     <row r="245" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A245" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B245" t="s">
         <v>2911</v>
@@ -44608,7 +44607,7 @@
     </row>
     <row r="246" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A246" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B246" t="s">
         <v>2911</v>
@@ -44751,7 +44750,7 @@
     </row>
     <row r="247" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A247" s="7" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>2912</v>
@@ -44894,7 +44893,7 @@
     </row>
     <row r="248" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>2912</v>
@@ -44945,7 +44944,7 @@
         <v>2186</v>
       </c>
       <c r="S248" s="2" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="T248" t="s">
         <v>2185</v>
@@ -45046,7 +45045,7 @@
     </row>
     <row r="249" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>2912</v>
@@ -45097,7 +45096,7 @@
         <v>2186</v>
       </c>
       <c r="S249" s="2" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="T249" t="s">
         <v>2185</v>
@@ -45339,7 +45338,7 @@
         <v>116</v>
       </c>
       <c r="BA250" s="2" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="251" spans="1:53" x14ac:dyDescent="0.2">
@@ -48581,7 +48580,7 @@
     </row>
     <row r="275" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A275" s="7" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="B275" t="s">
         <v>2911</v>
@@ -48721,7 +48720,7 @@
     </row>
     <row r="276" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="B276" t="s">
         <v>2911</v>
@@ -48864,7 +48863,7 @@
     </row>
     <row r="277" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="B277" t="s">
         <v>2911</v>
@@ -49004,7 +49003,7 @@
     </row>
     <row r="278" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A278" s="7" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="B278" t="s">
         <v>2911</v>
@@ -49046,7 +49045,7 @@
         <v>2160</v>
       </c>
       <c r="S278" s="2" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="T278" t="s">
         <v>2160</v>
@@ -49195,7 +49194,7 @@
         <v>1994</v>
       </c>
       <c r="S279" s="2" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="T279" t="s">
         <v>1995</v>
@@ -49347,7 +49346,7 @@
         <v>1976</v>
       </c>
       <c r="S280" s="2" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="T280" t="s">
         <v>1995</v>
@@ -51754,7 +51753,7 @@
     </row>
     <row r="297" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B297" t="s">
         <v>2911</v>
@@ -51894,7 +51893,7 @@
     </row>
     <row r="298" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B298" t="s">
         <v>2911</v>
@@ -52031,7 +52030,7 @@
     </row>
     <row r="299" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B299" t="s">
         <v>2911</v>
@@ -52168,7 +52167,7 @@
     </row>
     <row r="300" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B300" t="s">
         <v>2911</v>
@@ -52308,7 +52307,7 @@
     </row>
     <row r="301" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B301" t="s">
         <v>2911</v>
@@ -52445,7 +52444,7 @@
     </row>
     <row r="302" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>2912</v>
@@ -52582,7 +52581,7 @@
     </row>
     <row r="303" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>2912</v>
@@ -52722,7 +52721,7 @@
     </row>
     <row r="304" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B304" t="s">
         <v>2911</v>
@@ -52868,7 +52867,7 @@
     </row>
     <row r="305" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B305" t="s">
         <v>2911</v>
@@ -53011,7 +53010,7 @@
     </row>
     <row r="306" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B306" t="s">
         <v>2911</v>
@@ -53157,7 +53156,7 @@
     </row>
     <row r="307" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B307" t="s">
         <v>2911</v>
@@ -53300,7 +53299,7 @@
     </row>
     <row r="308" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B308" t="s">
         <v>2911</v>
@@ -53446,7 +53445,7 @@
     </row>
     <row r="309" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B309" t="s">
         <v>2911</v>
@@ -53589,7 +53588,7 @@
     </row>
     <row r="310" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B310" t="s">
         <v>2911</v>
@@ -53735,7 +53734,7 @@
     </row>
     <row r="311" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B311" t="s">
         <v>2911</v>
@@ -53872,7 +53871,7 @@
     </row>
     <row r="312" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B312" t="s">
         <v>2911</v>
@@ -54009,7 +54008,7 @@
     </row>
     <row r="313" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B313" t="s">
         <v>2911</v>
@@ -54146,7 +54145,7 @@
     </row>
     <row r="314" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B314" t="s">
         <v>2911</v>
@@ -54283,7 +54282,7 @@
     </row>
     <row r="315" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B315" t="s">
         <v>2911</v>
@@ -54423,7 +54422,7 @@
     </row>
     <row r="316" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B316" t="s">
         <v>2911</v>
@@ -54560,7 +54559,7 @@
     </row>
     <row r="317" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B317" t="s">
         <v>2911</v>
@@ -54691,7 +54690,7 @@
     </row>
     <row r="318" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B318" t="s">
         <v>2911</v>
@@ -54822,7 +54821,7 @@
     </row>
     <row r="319" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B319" t="s">
         <v>2911</v>
@@ -54953,7 +54952,7 @@
     </row>
     <row r="320" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B320" t="s">
         <v>2911</v>
@@ -55084,7 +55083,7 @@
     </row>
     <row r="321" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B321" t="s">
         <v>2911</v>
@@ -55215,7 +55214,7 @@
     </row>
     <row r="322" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B322" t="s">
         <v>2911</v>
@@ -55349,7 +55348,7 @@
     </row>
     <row r="323" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B323" t="s">
         <v>2911</v>
@@ -55483,7 +55482,7 @@
     </row>
     <row r="324" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B324" t="s">
         <v>2911</v>
@@ -55617,7 +55616,7 @@
     </row>
     <row r="325" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B325" t="s">
         <v>2911</v>
@@ -55749,7 +55748,7 @@
     </row>
     <row r="326" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A326" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B326" t="s">
         <v>2911</v>
@@ -55881,7 +55880,7 @@
     </row>
     <row r="327" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B327" t="s">
         <v>2911</v>
@@ -56015,7 +56014,7 @@
     </row>
     <row r="328" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>2902</v>
@@ -56057,13 +56056,13 @@
         <v>125</v>
       </c>
       <c r="Q328" s="2" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="R328" s="2" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="S328" s="2" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="V328" t="s">
         <v>59</v>
@@ -56161,7 +56160,7 @@
     </row>
     <row r="329" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B329" t="s">
         <v>2911</v>
@@ -56304,7 +56303,7 @@
     </row>
     <row r="330" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B330" t="s">
         <v>2911</v>
@@ -56447,7 +56446,7 @@
     </row>
     <row r="331" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B331" t="s">
         <v>2911</v>
@@ -56593,7 +56592,7 @@
     </row>
     <row r="332" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B332" t="s">
         <v>2911</v>
@@ -61708,7 +61707,7 @@
       </c>
     </row>
     <row r="367" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A367" s="9" t="s">
+      <c r="A367" s="8" t="s">
         <v>2321</v>
       </c>
       <c r="B367" t="s">
@@ -61757,7 +61756,7 @@
         <v>2307</v>
       </c>
       <c r="S367" s="2" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="V367" t="s">
         <v>59</v>
@@ -61854,8 +61853,8 @@
       </c>
     </row>
     <row r="368" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A368" s="8" t="s">
-        <v>2934</v>
+      <c r="A368" t="s">
+        <v>2933</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>2902</v>
@@ -61897,7 +61896,7 @@
         <v>2486</v>
       </c>
       <c r="S368" s="2" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="T368" t="s">
         <v>2486</v>

--- a/source_data/Cruaud_taxonomy_coi_min_bc_cov_300_seq_meta_updated.xlsx
+++ b/source_data/Cruaud_taxonomy_coi_min_bc_cov_300_seq_meta_updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ronquist/dev/ms-repos-iba/paper-mg-insects/source_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D6F668-0F95-C342-B9A3-2E1436F56B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0171199E-22E0-D245-BBFB-D983B7AABC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="500" windowWidth="28480" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="320" yWindow="500" windowWidth="28480" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cruaud_taxonomy_coi_min_bc_cov_" sheetId="1" r:id="rId1"/>
@@ -43258,7 +43258,7 @@
     </row>
     <row r="236" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A236" s="7" t="s">
-        <v>2929</v>
+        <v>1236</v>
       </c>
       <c r="B236" t="s">
         <v>2911</v>
@@ -43401,7 +43401,7 @@
     </row>
     <row r="237" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A237" s="7" t="s">
-        <v>2929</v>
+        <v>1236</v>
       </c>
       <c r="B237" t="s">
         <v>2911</v>
